--- a/output/independent-code-review/claude/sample-4/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-4/workpaper.xlsx
@@ -11,7 +11,6 @@
     <sheet name="Attribute Verdicts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence Inventory" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Decision Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,10 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
-  </numFmts>
-  <fonts count="14">
+  <numFmts count="0"/>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,10 +97,6 @@
       <b val="1"/>
       <color rgb="00A17321"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="5">
@@ -199,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,11 +222,6 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1363,838 +1351,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="15" t="inlineStr">
-        <is>
-          <t>Timestamp</t>
-        </is>
-      </c>
-      <c r="C1" s="15" t="inlineStr">
-        <is>
-          <t>Purpose</t>
-        </is>
-      </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="E1" s="15" t="inlineStr">
-        <is>
-          <t>Input tokens</t>
-        </is>
-      </c>
-      <c r="F1" s="15" t="inlineStr">
-        <is>
-          <t>Cache read</t>
-        </is>
-      </c>
-      <c r="G1" s="15" t="inlineStr">
-        <is>
-          <t>Output tokens</t>
-        </is>
-      </c>
-      <c r="H1" s="15" t="inlineStr">
-        <is>
-          <t>Cost USD</t>
-        </is>
-      </c>
-      <c r="I1" s="15" t="inlineStr">
-        <is>
-          <t>Latency (ms)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:48:14.126718Z</t>
-        </is>
-      </c>
-      <c r="C2" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
-        </is>
-      </c>
-      <c r="D2" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>6675</v>
-      </c>
-      <c r="F2" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="16" t="n">
-        <v>1787</v>
-      </c>
-      <c r="H2" s="19" t="n">
-        <v>0.23415</v>
-      </c>
-      <c r="I2" s="16" t="n">
-        <v>25332</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:48:39.485414Z</t>
-        </is>
-      </c>
-      <c r="C3" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="n">
-        <v>7348</v>
-      </c>
-      <c r="F3" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="16" t="n">
-        <v>1988</v>
-      </c>
-      <c r="H3" s="19" t="n">
-        <v>0.25932</v>
-      </c>
-      <c r="I3" s="16" t="n">
-        <v>25349</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:00.506620Z</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="n">
-        <v>7300</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>1515</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>0.223125</v>
-      </c>
-      <c r="I4" s="16" t="n">
-        <v>21014</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:13.305737Z</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-1</t>
-        </is>
-      </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>6270</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>1005</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.119934</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>12795</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:26.208418Z</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-1</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>6246</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>1092</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.126099</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>12900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:49:45.900071Z</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-1</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>8041</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>1578</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.189474</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>19689</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:10.052239Z</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>7264</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>1616</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>0.23016</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>24142</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:31.032351Z</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>7295</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>1504</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.222225</v>
-      </c>
-      <c r="I9" s="16" t="n">
-        <v>20969</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:44.382655Z</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-2</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>4057</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>1067</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.091389</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <v>13346</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:50:57.753305Z</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-2</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>4033</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>1108</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.09410399999999999</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>13368</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:51:17.209066Z</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-2</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>5828</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>1487</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>0.149454</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>19453</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:51:31.339364Z</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:kubernetes-pr-checks.png</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>4703</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>945</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>0.14142</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <v>14122</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:52:34.116483Z</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:kubernetes-pr.png</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>4172</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>4640</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <v>0.41058</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <v>62769</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:52:46.504782Z</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-3</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>6582</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>1002</v>
-      </c>
-      <c r="H15" s="19" t="n">
-        <v>0.124389</v>
-      </c>
-      <c r="I15" s="16" t="n">
-        <v>12384</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:04.324724Z</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-3</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>6558</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>1257</v>
-      </c>
-      <c r="H16" s="19" t="n">
-        <v>0.143154</v>
-      </c>
-      <c r="I16" s="16" t="n">
-        <v>17817</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:22.086254Z</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-3</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>8353</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>1369</v>
-      </c>
-      <c r="H17" s="19" t="n">
-        <v>0.178479</v>
-      </c>
-      <c r="I17" s="16" t="n">
-        <v>17758</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:53:36.065782Z</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:nextjs-pr-checks.png</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>4702</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>924</v>
-      </c>
-      <c r="H18" s="19" t="n">
-        <v>0.13983</v>
-      </c>
-      <c r="I18" s="16" t="n">
-        <v>13972</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:01.769450Z</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>screenshot:nextjs-pr.png</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>6103</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>1808</v>
-      </c>
-      <c r="H19" s="19" t="n">
-        <v>0.227145</v>
-      </c>
-      <c r="I19" s="16" t="n">
-        <v>25696</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:15.073618Z</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>judge:code-review-prior-to-merge:sample-4</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>3730</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>989</v>
-      </c>
-      <c r="H20" s="19" t="n">
-        <v>0.080634</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>13300</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:26.858373Z</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>judge:independent-reviewer-approval:sample-4</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>3706</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>902</v>
-      </c>
-      <c r="H21" s="19" t="n">
-        <v>0.073749</v>
-      </c>
-      <c r="I21" s="16" t="n">
-        <v>11782</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>2026-07-03T03:54:43.961668Z</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>judge:testing-per-policy:sample-4</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>claude-opus-4-7</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>5501</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>3666</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>1265</v>
-      </c>
-      <c r="H22" s="19" t="n">
-        <v>0.127899</v>
-      </c>
-      <c r="I22" s="16" t="n">
-        <v>17098</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E23" s="20">
-        <f>SUM(E2:E22)</f>
-        <v/>
-      </c>
-      <c r="F23" s="20">
-        <f>SUM(F2:F22)</f>
-        <v/>
-      </c>
-      <c r="G23" s="20">
-        <f>SUM(G2:G22)</f>
-        <v/>
-      </c>
-      <c r="H23" s="21">
-        <f>SUM(H2:H22)</f>
-        <v/>
-      </c>
-      <c r="I23" s="20">
-        <f>SUM(I2:I22)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/output/independent-code-review/claude/sample-4/workpaper.xlsx
+++ b/output/independent-code-review/claude/sample-4/workpaper.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Attribute Verdicts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Evidence Citations" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidence Inventory" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Decision Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,8 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="13">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
+  </numFmts>
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -97,6 +100,10 @@
       <b val="1"/>
       <color rgb="00A17321"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000B362C"/>
     </font>
   </fonts>
   <fills count="5">
@@ -192,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -222,6 +229,11 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -642,7 +654,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>claude:claude-opus-4-7</t>
+          <t>claude:claude-opus-4-8</t>
         </is>
       </c>
     </row>
@@ -654,7 +666,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>03 Jul 2026, 03:54 UTC</t>
+          <t>03 Jul 2026, 04:21 UTC</t>
         </is>
       </c>
     </row>
@@ -730,7 +742,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The evidence shows CI ran (130 checks, 129 passed) and a "Tests Passed" bot comment on commit f059653, but no coverage report is present in the bundle.</t>
+          <t>Provide additional evidence to close “Testing is performed in accordance with the testing policy”. Specifically: The change touches production code (+367/-15 across 8 files fixing router navigation behavior), so no policy exception (documentation-only, dependency bump, refactor, etc.</t>
         </is>
       </c>
     </row>
@@ -872,11 +884,11 @@
         </is>
       </c>
       <c r="C2" s="16" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>A pull request (#95391) exists for the change, satisfying the review-record criterion. Two approvals are recorded — gnoff "approved these changes yesterday" and acdlite "approved these changes 12 hours ago" — both prior to the merge which occurred "4 hours ago". The PR shows "gaearon merged 6 commits into canary" with merge commit db4e623, indicating the change went through PR review rather than a direct commit to the target branch. Relative timestamps consistently place approvals before merge, so the ordering criterion is met.</t>
+          <t>A pull request review record exists: the Reviewers panel lists gnoff and acdlite, each with green checkmarks, and both explicitly approved ("gnoff approved these changes yesterday", "acdlite approved these changes 12 hours ago"). Both approvals precede the merge, which occurred "4 hours ago" — the approval timestamps (yesterday and 12 hours ago) are both earlier than the 4-hours-ago merge. The change was merged only after both approvals were in place ("gaearon merged commit db4e623 into canary 4 hours ago"), demonstrating review occurred prior to committing to the target branch. The one caveat is that "canary" (not "main") is the target branch, but it is the integration branch to which this change was merged post-review.</t>
         </is>
       </c>
       <c r="E2" s="16" t="n">
@@ -884,7 +896,7 @@
       </c>
       <c r="F2" s="16" t="inlineStr">
         <is>
-          <t>Target branch is 'canary' rather than 'main'/'master'; in the next.js repo canary is the active integration branch that the PR was merged into, which is the branch analogous to 'main' for this attribute. The attribute concerns merging via reviewed PR rather than direct commit, and that condition is satisfied.</t>
+          <t>Target branch is 'canary' rather than 'main' — accepted as the effective integration branch for this repo; review clearly preceded the merge, satisfying the 'prior to committing' intent.</t>
         </is>
       </c>
     </row>
@@ -904,15 +916,15 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>The PR was authored and merged by gaearon, and two distinct human reviewers (gnoff and acdlite) approved the changes prior to merge — gnoff approved "yesterday" and acdlite approved "12 hours ago", both before the merge that occurred "4 hours ago". Neither approver appears as an author or committer on any of the six commits (all commits are attributed to gaearon). Both approvals are recorded with green check marks in the Reviewers panel, satisfying the 4-eyes principle with independent human reviewers (not bots).</t>
+          <t>The PR author/committer is 'gaearon' (opened the PR, force-pushed commits, and merged). Two distinct human reviewers, 'gnoff' and 'acdlite', each approved the changes with green checkmarks — both are different individuals from the author and neither has an authorship/committer role. The 4-eyes principle is satisfied by at least two independent human approvals (not bots). The github-actions Bot comments are correctly disregarded as non-human.</t>
         </is>
       </c>
       <c r="E3" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>Considered whether either approver could be a bot — both gnoff and acdlite are named human GitHub handles (acdlite left a substantive review comment about test compatibility), distinct from the github-actions[bot] which only posted status messages.</t>
+          <t>Considered whether approvers were bots — github-actions is a Bot and was excluded; gnoff and acdlite are human reviewers, so independence holds.</t>
         </is>
       </c>
     </row>
@@ -928,11 +940,11 @@
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>The evidence shows CI ran (130 checks, 129 passed) and a "Tests Passed" bot comment on commit f059653, but no coverage report is present in the bundle. I cannot verify the policy thresholds (≥80% line, ≥70% branch, ≥80% function, ≥60% integration, 100% for security/auth/payment paths). Additionally, one of 130 checks did not pass ("129 of 130 checks passed") and its status (failure vs. cancellation, e.g. the "Stats cancelled" bot comment) is not visible, so I cannot confirm "zero failures". A coverage report screenshot for this PR's CI run and clarification of the single non-passing check would resolve this to SUCCESS.</t>
+          <t>The change touches production code (+367/-15 across 8 files fixing router navigation behavior), so no policy exception (documentation-only, dependency bump, refactor, etc.) applies. Evidence shows tests ran in CI and a bot comment "Tests Passed", with "129 of 130 checks passed" at merge — but no coverage report is present in the bundle, so I cannot verify the ≥80% line, ≥70% branch, ≥80% function, or 100% critical-path thresholds required by the testing policy. Additionally, two commits (13b2539 and f059653) show a red X next to Verified and the summary shows 1 of 130 checks not passing, and the failing check is not readable — leaving unit/integration/e2e pass status unconfirmed. A coverage report screenshot for this PR's final run plus the identity of the single failing check would resolve this to SUCCESS or FAIL.</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
@@ -940,7 +952,8 @@
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>Behavior-preserving refactor / documentation-only exceptions considered and rejected — the PR fixes a functional bug (navigation reverting during Server Action) and adds +367 lines including new tests and production code changes, so it does not qualify as an exempt category.</t>
+          <t>Documentation-only / refactor / dependency-bump exceptions — rejected: PR changes production router logic with +367/-15 across 8 files, which is a behavioral change, not exempt.
+Test-only maintenance — rejected: production source files are modified, not solely test files.</t>
         </is>
       </c>
     </row>
@@ -955,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -999,12 +1012,12 @@
       </c>
       <c r="C2" s="16" t="inlineStr">
         <is>
-          <t>PR header / merge status line</t>
+          <t>Reviewers side panel</t>
         </is>
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>'gaearon merged 6 commits into canary from gaearon-fix-reverting-nav 4 hours ago' with purple 'Merged' badge and merge commit db4e623 — change entered the target branch via PR merge.</t>
+          <t>Reviewers gnoff and acdlite each shown with a green checkmark, indicating approving reviews exist.</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1034,12 @@
       </c>
       <c r="C3" s="16" t="inlineStr">
         <is>
-          <t>Reviewers side panel and timeline</t>
+          <t>Conversation timeline — approval events</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>Reviewers panel shows gnoff and acdlite with green checks; timeline states 'gnoff approved these changes yesterday' and 'acdlite approved these changes 12 hours ago'.</t>
+          <t>'gnoff approved these changes yesterday' and 'acdlite approved these changes 12 hours ago', both with green checks.</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1056,12 @@
       </c>
       <c r="C4" s="16" t="inlineStr">
         <is>
-          <t>Timeline ordering of approvals vs merge</t>
+          <t>Merge footer line</t>
         </is>
       </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
-          <t>Approvals timestamped 'yesterday' and '12 hours ago' both precede the merge event '4 hours ago', so approval preceded merge to canary.</t>
+          <t>'gaearon merged commit db4e623 into canary 4 hours ago' — merge occurred after both approvals (yesterday / 12 hours ago), so approval timestamps precede the merge.</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1073,17 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>nextjs-pr-checks.png</t>
+          <t>nextjs-pr.png</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>PR header</t>
+          <t>PR header / merge line</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
         <is>
-          <t>Confirms same PR #95391 exists with 'Merged' status and 6 commits merged from feature branch gaearon-fix-reverting-nav into canary — a PR-based (non-direct) path to the branch.</t>
+          <t>Purple 'Merged' badge and '129 of 130 checks passed' at merge, confirming the PR was merged only after the review workflow completed.</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1100,12 @@
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
-          <t>Reviewers side panel</t>
+          <t>Merge footer line</t>
         </is>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>Two reviewers listed with green check marks: 'gnoff' and 'acdlite'</t>
+          <t>'gaearon merged 6 commits into canary' and 'gaearon force-pushed' — gaearon is the author/committer of the change.</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1122,12 @@
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
-          <t>Merge status line at bottom of conversation</t>
+          <t>Reviewers side panel</t>
         </is>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>'gaearon merged 6 commits into canary from gaearon-fix-reverting-nav 4 hours ago' — identifies gaearon as author/merger</t>
+          <t>'gnoff' and 'acdlite' listed as reviewers, each with a green checkmark indicating approval.</t>
         </is>
       </c>
     </row>
@@ -1131,19 +1144,19 @@
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
-          <t>Conversation timeline — approval events</t>
+          <t>Conversation timeline (approval events)</t>
         </is>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>'gnoff approved these changes yesterday' and 'acdlite approved these changes 12 hours ago' — both occurred prior to the merge 4 hours ago</t>
+          <t>'gnoff approved these changes yesterday' and 'acdlite approved these changes 12 hours ago', both with green checks — two distinct human approvers separate from gaearon.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>Code Review approvals are performed by independent code reviewers</t>
+          <t>Testing is performed in accordance with the testing policy</t>
         </is>
       </c>
       <c r="B9" s="16" t="inlineStr">
@@ -1153,12 +1166,12 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>Commits list in conversation timeline</t>
+          <t>Diff stat / Files changed tab header</t>
         </is>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>All six commits (bf31625, 13b2539, 44b9cad, a459e9d, 38f1201, f059653) attributed to gaearon; no commits from gnoff or acdlite</t>
+          <t>PR modifies production code (+367 -15 across 8 files) fixing router navigation behavior — not a documentation-only or refactor change, so no testing-policy exception applies.</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1188,12 @@
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
-          <t>Merge status area / checks summary line</t>
+          <t>github-actions bot comment and merge status line</t>
         </is>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>'129 of 130 checks passed' displayed below the merge line — one check is not accounted for; no coverage percentages visible.</t>
+          <t>Bot comment 'Tests Passed' for commit f059653 and '129 of 130 checks passed' shown at merge — 1 check did not pass and the failing check identity is not readable.</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1210,12 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>Timeline — github-actions[bot] comments on commit f059653</t>
+          <t>Commit list rows for 13b2539 and f059653</t>
         </is>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Two bot comments visible: 'Tests Passed' and 'Stats cancelled' — indicates tests ran and passed, but 'Stats cancelled' suggests one workflow was cancelled rather than passed.</t>
+          <t>Two commits show a red X next to the Verified badge, indicating a failed check; exact failing check not identifiable from the image.</t>
         </is>
       </c>
     </row>
@@ -1219,34 +1232,12 @@
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>Checks tab — right pane</t>
+          <t>Checks tab / right panel</t>
         </is>
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>Right pane shows placeholder 'Select a check to view from the sidebar'; no individual check statuses, no coverage report artefact visible. Annotation counts (1, 4, 34) shown for some workflow groups but no coverage numbers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Testing is performed in accordance with the testing policy</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>nextjs-pr.png</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>Files changed / diff summary header</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Diff is +367 / -15 across 8 files including test/e2e/app-dir/actions-discarded-navigation-revert paths — indicates new tests were added, but coverage % for new code is not reported anywhere in evidence.</t>
+          <t>Checks tab shows 130 checks with annotation counts but right panel reads 'Select a check to view from the sidebar'; no coverage report or per-check pass/fail detail is visible.</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1305,12 @@
       </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
-          <t>GitHub Pull Request page — Checks tab · 11 facts extracted · 2 people · 4 ambiguity flag(s)</t>
+          <t>GitHub Pull Request page — "Checks" tab · 15 facts extracted · 1 people · 5 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>code-review-prior-to-merge, testing-per-policy</t>
+          <t>testing-per-testing-policy</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1330,847 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>GitHub Pull Request page · 26 facts extracted · 9 people · 5 ambiguity flag(s)</t>
+          <t>GitHub Pull Request page (vercel/next.js, PR #95391) · 30 facts extracted · 9 people · 5 ambiguity flag(s)</t>
         </is>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>code-review-prior-to-merge, code-review-prior-to-merge, code-review-prior-to-merge, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-policy, testing-per-policy, testing-per-policy</t>
-        </is>
+          <t>code-review-before-commit-to-main, code-review-before-commit-to-main, code-review-before-commit-to-main, code-review-before-commit-to-main, independent-reviewer-approval, independent-reviewer-approval, independent-reviewer-approval, testing-per-testing-policy, testing-per-testing-policy, testing-per-testing-policy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>Input tokens</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>Cache read</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>Output tokens</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>Cost USD</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>Latency (ms)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:15:40.084130Z</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-27-50 Coverage Report.png</t>
+        </is>
+      </c>
+      <c r="D2" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E2" s="16" t="n">
+        <v>4474</v>
+      </c>
+      <c r="F2" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="16" t="n">
+        <v>1660</v>
+      </c>
+      <c r="H2" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="16" t="n">
+        <v>23603</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:06.122392Z</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-28-31 Shrink relationComplexityError test size by jakebailey · Pull Request #62754 · microsoft_TypeScript.png</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="n">
+        <v>5147</v>
+      </c>
+      <c r="F3" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G3" s="16" t="n">
+        <v>2338</v>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="16" t="n">
+        <v>26026</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:30.394765Z</t>
+        </is>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-29-21 Shrink relationComplexityError test size · microsoft_TypeScript@9e76dd2.png</t>
+        </is>
+      </c>
+      <c r="D4" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>5099</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>1763</v>
+      </c>
+      <c r="H4" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="16" t="n">
+        <v>24264</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:44.295721Z</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-1</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>6383</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>1065</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="16" t="n">
+        <v>13897</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:16:55.782597Z</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-1</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>6355</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>927</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="16" t="n">
+        <v>11484</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:11.438826Z</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-1</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>8116</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>1317</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>15655</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:34.006071Z</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-31-38 feat use Node.js timers by default · denoland_deno@12cde71.png</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>5063</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>1746</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>22559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:17:57.834234Z</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:Screenshot 2025-11-14 at 14-32-05 feat use Node.js timers by default by bartlomieju · Pull Request #31272 · denoland_deno.png</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>5094</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>1921</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="16" t="n">
+        <v>23819</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:09.107798Z</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-2</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>4233</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>946</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="16" t="n">
+        <v>11269</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:20.213919Z</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-2</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>4205</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>943</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>11102</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:39.404920Z</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-2</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>1616</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>19186</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:18:52.612761Z</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>2502</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>963</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>13198</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:22.610986Z</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:kubernetes-pr.png</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="n">
+        <v>1971</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G14" s="16" t="n">
+        <v>2247</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>29989</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:35.659572Z</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-3</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>3818</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>1030</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="16" t="n">
+        <v>13044</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:19:48.832139Z</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-3</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>3790</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>994</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>13169</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:03.784191Z</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-3</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E17" s="16" t="n">
+        <v>5551</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G17" s="16" t="n">
+        <v>1256</v>
+      </c>
+      <c r="H17" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="16" t="n">
+        <v>14948</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:18.239343Z</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr-checks.png</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="n">
+        <v>2501</v>
+      </c>
+      <c r="F18" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G18" s="16" t="n">
+        <v>1103</v>
+      </c>
+      <c r="H18" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="16" t="n">
+        <v>14446</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:41.669803Z</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>screenshot:nextjs-pr.png</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E19" s="16" t="n">
+        <v>3902</v>
+      </c>
+      <c r="F19" s="16" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <v>1798</v>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="16" t="n">
+        <v>23426</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:20:53.838524Z</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>judge:code-review-before-commit-to-main:sample-4</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>3513</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <v>912</v>
+      </c>
+      <c r="H20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="16" t="n">
+        <v>12165</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:21:02.663985Z</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>judge:independent-reviewer-approval:sample-4</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>3485</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G21" s="16" t="n">
+        <v>711</v>
+      </c>
+      <c r="H21" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="16" t="n">
+        <v>8821</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-03T04:21:19.635538Z</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>judge:testing-per-testing-policy:sample-4</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>5246</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>5151</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>1284</v>
+      </c>
+      <c r="H22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="16" t="n">
+        <v>16967</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="E23" s="20">
+        <f>SUM(E2:E22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="20">
+        <f>SUM(F2:F22)</f>
+        <v/>
+      </c>
+      <c r="G23" s="20">
+        <f>SUM(G2:G22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="21">
+        <f>SUM(H2:H22)</f>
+        <v/>
+      </c>
+      <c r="I23" s="20">
+        <f>SUM(I2:I22)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
